--- a/FUTURE_USERS_LOOK_HERE/tutors.xlsx
+++ b/FUTURE_USERS_LOOK_HERE/tutors.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,6 +440,9 @@
       <c r="M1" t="str">
         <v>Avaliable</v>
       </c>
+      <c r="N1" t="str">
+        <v>Photo Filename</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -458,28 +461,31 @@
         <v>12</v>
       </c>
       <c r="F2" t="str">
-        <v>Algebra 1, Algebra 1 H, Algebra 2, Algebra 2 W/ Trig, Geometry, Pre-Calculus, Pre-Calculus H</v>
+        <v>Algebra 1</v>
       </c>
       <c r="G2" t="str">
-        <v>Freshman STEM</v>
+        <v>Algebra 1 H</v>
       </c>
       <c r="H2" t="str">
-        <v>World History, United States History, Civics</v>
+        <v>Algebra 2</v>
       </c>
       <c r="I2" t="str">
-        <v>Spanish 1</v>
+        <v>Algebra 2 W/ Trig</v>
       </c>
       <c r="J2" t="str">
-        <v>AP Computer Science Principles, AP Computer Science A, Intro to Computer Science</v>
+        <v>Geometry</v>
       </c>
       <c r="K2" t="str">
-        <v>English 1, English 2, English 3</v>
+        <v>Pre-Calculus</v>
       </c>
       <c r="L2" t="str">
-        <v>Farenheit 451, Ender's Game, Catcher in the Rye, Julius Caesar, Lord of the Flies, The Great Gatsby, Into the Wild</v>
+        <v>Pre-Calculus H</v>
       </c>
       <c r="M2" t="str">
         <v>false</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Aidan Loberg.jpeg</v>
       </c>
     </row>
     <row r="3">
@@ -522,6 +528,9 @@
       <c r="M3" t="str">
         <v>false</v>
       </c>
+      <c r="N3" t="str">
+        <v>Brady Lyons.jpeg</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -563,6 +572,9 @@
       <c r="M4" t="str">
         <v>false</v>
       </c>
+      <c r="N4" t="str">
+        <v>Brayden Berry.jpeg</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -604,6 +616,9 @@
       <c r="M5" t="str">
         <v>false</v>
       </c>
+      <c r="N5" t="str">
+        <v>Clyde Ramos.jpeg</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -645,6 +660,9 @@
       <c r="M6" t="str">
         <v>false</v>
       </c>
+      <c r="N6" t="str">
+        <v>Danny Accardo.jpeg</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -686,6 +704,9 @@
       <c r="M7" t="str">
         <v>false</v>
       </c>
+      <c r="N7" t="str">
+        <v>Derrick Bajada.jpeg</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -727,6 +748,9 @@
       <c r="M8" t="str">
         <v>false</v>
       </c>
+      <c r="N8" t="str">
+        <v>Dillon Gaber.jpeg</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -768,6 +792,9 @@
       <c r="M9" t="str">
         <v>false</v>
       </c>
+      <c r="N9" t="str">
+        <v>Ernest Lizardo.jpeg</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -809,6 +836,9 @@
       <c r="M10" t="str">
         <v>false</v>
       </c>
+      <c r="N10" t="str">
+        <v>Gijo Cunanan.jpeg</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -850,6 +880,9 @@
       <c r="M11" t="str">
         <v>false</v>
       </c>
+      <c r="N11" t="str">
+        <v>Heath Salter.jpeg</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -891,6 +924,9 @@
       <c r="M12" t="str">
         <v>false</v>
       </c>
+      <c r="N12" t="str">
+        <v>Hudson Lee.jpeg</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -932,6 +968,9 @@
       <c r="M13" t="str">
         <v>false</v>
       </c>
+      <c r="N13" t="str">
+        <v>Hugh Arnold.jpeg</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -973,6 +1012,9 @@
       <c r="M14" t="str">
         <v>false</v>
       </c>
+      <c r="N14" t="str">
+        <v>Ivo Nuti.jpeg</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1014,6 +1056,9 @@
       <c r="M15" t="str">
         <v>false</v>
       </c>
+      <c r="N15" t="str">
+        <v>Jack Chlebicki.jpeg</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1055,6 +1100,9 @@
       <c r="M16" t="str">
         <v>false</v>
       </c>
+      <c r="N16" t="str">
+        <v>Jack Throne.jpeg</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1096,6 +1144,9 @@
       <c r="M17" t="str">
         <v>false</v>
       </c>
+      <c r="N17" t="str">
+        <v>Joe Bindi.jpeg</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1137,6 +1188,9 @@
       <c r="M18" t="str">
         <v>false</v>
       </c>
+      <c r="N18" t="str">
+        <v>John Gregory.jpeg</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1178,6 +1232,9 @@
       <c r="M19" t="str">
         <v>false</v>
       </c>
+      <c r="N19" t="str">
+        <v>Johnny Cumbelich.jpeg</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1219,6 +1276,9 @@
       <c r="M20" t="str">
         <v>false</v>
       </c>
+      <c r="N20" t="str">
+        <v>Jonah Ribando.jpeg</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1260,6 +1320,9 @@
       <c r="M21" t="str">
         <v>false</v>
       </c>
+      <c r="N21" t="str">
+        <v>Joshua Truman.jpeg</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1301,6 +1364,9 @@
       <c r="M22" t="str">
         <v>false</v>
       </c>
+      <c r="N22" t="str">
+        <v>Kellen Dunn.jpeg</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1342,6 +1408,9 @@
       <c r="M23" t="str">
         <v>false</v>
       </c>
+      <c r="N23" t="str">
+        <v>Kenz Mogannam.jpeg</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1383,6 +1452,9 @@
       <c r="M24" t="str">
         <v>false</v>
       </c>
+      <c r="N24" t="str">
+        <v>Lee Vaouli.jpeg</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1424,6 +1496,9 @@
       <c r="M25" t="str">
         <v>false</v>
       </c>
+      <c r="N25" t="str">
+        <v>Leonardo Massa.jpeg</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1465,6 +1540,9 @@
       <c r="M26" t="str">
         <v>false</v>
       </c>
+      <c r="N26" t="str">
+        <v>Logan Waters.jpeg</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1506,6 +1584,9 @@
       <c r="M27" t="str">
         <v>false</v>
       </c>
+      <c r="N27" t="str">
+        <v>Luciano Crews.jpeg</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1547,6 +1628,9 @@
       <c r="M28" t="str">
         <v>false</v>
       </c>
+      <c r="N28" t="str">
+        <v>Matthew Angerame.jpeg</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1588,6 +1672,9 @@
       <c r="M29" t="str">
         <v>false</v>
       </c>
+      <c r="N29" t="str">
+        <v>Matthew Dwinell.jpeg</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1629,6 +1716,9 @@
       <c r="M30" t="str">
         <v>false</v>
       </c>
+      <c r="N30" t="str">
+        <v>Max Munzinger.jpeg</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1670,6 +1760,9 @@
       <c r="M31" t="str">
         <v>false</v>
       </c>
+      <c r="N31" t="str">
+        <v>Nicholas Costagliola.jpeg</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1711,6 +1804,9 @@
       <c r="M32" t="str">
         <v>false</v>
       </c>
+      <c r="N32" t="str">
+        <v>Nicholas Parker.jpeg</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1752,6 +1848,9 @@
       <c r="M33" t="str">
         <v>false</v>
       </c>
+      <c r="N33" t="str">
+        <v>Nio Estacio.jpeg</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1793,6 +1892,9 @@
       <c r="M34" t="str">
         <v>false</v>
       </c>
+      <c r="N34" t="str">
+        <v>Peter Kroger.jpeg</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1834,6 +1936,9 @@
       <c r="M35" t="str">
         <v>false</v>
       </c>
+      <c r="N35" t="str">
+        <v>Reese Roque.jpeg</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1875,6 +1980,9 @@
       <c r="M36" t="str">
         <v>false</v>
       </c>
+      <c r="N36" t="str">
+        <v>Sean Edens.jpeg</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1916,6 +2024,9 @@
       <c r="M37" t="str">
         <v>false</v>
       </c>
+      <c r="N37" t="str">
+        <v>Tanner Lustig.jpeg</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1957,6 +2068,9 @@
       <c r="M38" t="str">
         <v>false</v>
       </c>
+      <c r="N38" t="str">
+        <v>Theo Widjaja.jpeg</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1998,6 +2112,9 @@
       <c r="M39" t="str">
         <v>false</v>
       </c>
+      <c r="N39" t="str">
+        <v>Turner Madge.jpeg</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2039,6 +2156,9 @@
       <c r="M40" t="str">
         <v>false</v>
       </c>
+      <c r="N40" t="str">
+        <v>Tyce Di Pretoro.jpeg</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2080,6 +2200,9 @@
       <c r="M41" t="str">
         <v>false</v>
       </c>
+      <c r="N41" t="str">
+        <v>Aldo Gonzalez.jpeg</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -2121,6 +2244,9 @@
       <c r="M42" t="str">
         <v>false</v>
       </c>
+      <c r="N42" t="str">
+        <v>Alex Lordan.jpeg</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2162,6 +2288,9 @@
       <c r="M43" t="str">
         <v>false</v>
       </c>
+      <c r="N43" t="str">
+        <v>Angel Molina-Oncena.jpeg</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2203,6 +2332,9 @@
       <c r="M44" t="str">
         <v>false</v>
       </c>
+      <c r="N44" t="str">
+        <v>Anthony Dumais.jpeg</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2244,6 +2376,9 @@
       <c r="M45" t="str">
         <v>false</v>
       </c>
+      <c r="N45" t="str">
+        <v>Antony Abudayeh.jpeg</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2285,6 +2420,9 @@
       <c r="M46" t="str">
         <v>false</v>
       </c>
+      <c r="N46" t="str">
+        <v>Bryce Norrett.jpeg</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -2326,6 +2464,9 @@
       <c r="M47" t="str">
         <v>false</v>
       </c>
+      <c r="N47" t="str">
+        <v>Bryson Cooper.jpeg</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -2367,6 +2508,9 @@
       <c r="M48" t="str">
         <v>false</v>
       </c>
+      <c r="N48" t="str">
+        <v>Carson mucha.jpeg</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2408,6 +2552,9 @@
       <c r="M49" t="str">
         <v>false</v>
       </c>
+      <c r="N49" t="str">
+        <v>Carver Dixon.jpeg</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2449,6 +2596,9 @@
       <c r="M50" t="str">
         <v>false</v>
       </c>
+      <c r="N50" t="str">
+        <v>Clint Lundin.jpeg</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -2490,6 +2640,9 @@
       <c r="M51" t="str">
         <v>false</v>
       </c>
+      <c r="N51" t="str">
+        <v>David Hanley.jpeg</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -2531,6 +2684,9 @@
       <c r="M52" t="str">
         <v>false</v>
       </c>
+      <c r="N52" t="str">
+        <v>Dylan Pugay.jpeg</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -2572,6 +2728,9 @@
       <c r="M53" t="str">
         <v>false</v>
       </c>
+      <c r="N53" t="str">
+        <v>Ellis Toal.jpeg</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -2613,6 +2772,9 @@
       <c r="M54" t="str">
         <v>false</v>
       </c>
+      <c r="N54" t="str">
+        <v>Emmanuel Di Giusto.jpeg</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -2654,6 +2816,9 @@
       <c r="M55" t="str">
         <v>false</v>
       </c>
+      <c r="N55" t="str">
+        <v>Ethan Crossett.jpeg</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -2695,6 +2860,9 @@
       <c r="M56" t="str">
         <v>false</v>
       </c>
+      <c r="N56" t="str">
+        <v>Ethan Joshi.jpeg</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -2736,6 +2904,9 @@
       <c r="M57" t="str">
         <v>false</v>
       </c>
+      <c r="N57" t="str">
+        <v>Evan Mims.jpeg</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -2777,6 +2948,9 @@
       <c r="M58" t="str">
         <v>false</v>
       </c>
+      <c r="N58" t="str">
+        <v>Flynn Salyapongse.jpeg</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -2818,6 +2992,9 @@
       <c r="M59" t="str">
         <v>false</v>
       </c>
+      <c r="N59" t="str">
+        <v>Frank Cattrone.jpeg</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -2859,6 +3036,9 @@
       <c r="M60" t="str">
         <v>false</v>
       </c>
+      <c r="N60" t="str">
+        <v>Gerard Andico.jpeg</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -2900,6 +3080,9 @@
       <c r="M61" t="str">
         <v>false</v>
       </c>
+      <c r="N61" t="str">
+        <v>Jack McPhee.jpeg</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2941,6 +3124,9 @@
       <c r="M62" t="str">
         <v>false</v>
       </c>
+      <c r="N62" t="str">
+        <v>Jacob Dionson.jpeg</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2982,6 +3168,9 @@
       <c r="M63" t="str">
         <v>false</v>
       </c>
+      <c r="N63" t="str">
+        <v>Jacob Nguyen.jpeg</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3023,6 +3212,9 @@
       <c r="M64" t="str">
         <v>false</v>
       </c>
+      <c r="N64" t="str">
+        <v>Joshua McGrath.jpeg</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -3064,6 +3256,9 @@
       <c r="M65" t="str">
         <v>false</v>
       </c>
+      <c r="N65" t="str">
+        <v>Joshua Symonds.jpeg</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -3105,6 +3300,9 @@
       <c r="M66" t="str">
         <v>false</v>
       </c>
+      <c r="N66" t="str">
+        <v>Kael Melaas.jpeg</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -3146,6 +3344,9 @@
       <c r="M67" t="str">
         <v>false</v>
       </c>
+      <c r="N67" t="str">
+        <v>Kieran Brosnan.jpeg</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -3187,6 +3388,9 @@
       <c r="M68" t="str">
         <v>false</v>
       </c>
+      <c r="N68" t="str">
+        <v>Kyle Guinto.jpeg</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -3228,6 +3432,9 @@
       <c r="M69" t="str">
         <v>false</v>
       </c>
+      <c r="N69" t="str">
+        <v>Lance Molina.jpeg</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -3269,6 +3476,9 @@
       <c r="M70" t="str">
         <v>false</v>
       </c>
+      <c r="N70" t="str">
+        <v>Luka Stark.jpeg</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -3310,6 +3520,9 @@
       <c r="M71" t="str">
         <v>false</v>
       </c>
+      <c r="N71" t="str">
+        <v>Luke Griffith.jpeg</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -3351,6 +3564,9 @@
       <c r="M72" t="str">
         <v>false</v>
       </c>
+      <c r="N72" t="str">
+        <v>Luke Huang.jpeg</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -3392,6 +3608,9 @@
       <c r="M73" t="str">
         <v>false</v>
       </c>
+      <c r="N73" t="str">
+        <v>Luke Johnson.jpeg</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -3433,6 +3652,9 @@
       <c r="M74" t="str">
         <v>false</v>
       </c>
+      <c r="N74" t="str">
+        <v>Marco Gnusti.jpeg</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -3474,6 +3696,9 @@
       <c r="M75" t="str">
         <v>false</v>
       </c>
+      <c r="N75" t="str">
+        <v>Matthew Gillette.jpeg</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -3515,6 +3740,9 @@
       <c r="M76" t="str">
         <v>false</v>
       </c>
+      <c r="N76" t="str">
+        <v>Michael Macri.jpeg</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -3556,6 +3784,9 @@
       <c r="M77" t="str">
         <v>false</v>
       </c>
+      <c r="N77" t="str">
+        <v>Nicholas Persi.jpeg</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -3597,6 +3828,9 @@
       <c r="M78" t="str">
         <v>false</v>
       </c>
+      <c r="N78" t="str">
+        <v>Nick Jensen.jpeg</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -3638,6 +3872,9 @@
       <c r="M79" t="str">
         <v>false</v>
       </c>
+      <c r="N79" t="str">
+        <v>Nicky Ertoz.jpeg</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -3679,6 +3916,9 @@
       <c r="M80" t="str">
         <v>false</v>
       </c>
+      <c r="N80" t="str">
+        <v>Rayne Gutierrez.jpeg</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -3720,6 +3960,9 @@
       <c r="M81" t="str">
         <v>false</v>
       </c>
+      <c r="N81" t="str">
+        <v>Reid Chapman.jpeg</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -3761,6 +4004,9 @@
       <c r="M82" t="str">
         <v>false</v>
       </c>
+      <c r="N82" t="str">
+        <v>Ryan Carrillo.jpeg</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -3802,6 +4048,9 @@
       <c r="M83" t="str">
         <v>false</v>
       </c>
+      <c r="N83" t="str">
+        <v>Ryan Donnelly.jpeg</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -3843,6 +4092,9 @@
       <c r="M84" t="str">
         <v>false</v>
       </c>
+      <c r="N84" t="str">
+        <v>Sebastian Cabrales.jpeg</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -3884,6 +4136,9 @@
       <c r="M85" t="str">
         <v>false</v>
       </c>
+      <c r="N85" t="str">
+        <v>Silas Wan.jpeg</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -3925,6 +4180,9 @@
       <c r="M86" t="str">
         <v>false</v>
       </c>
+      <c r="N86" t="str">
+        <v>Todd McClure.jpeg</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -3966,6 +4224,9 @@
       <c r="M87" t="str">
         <v>false</v>
       </c>
+      <c r="N87" t="str">
+        <v>Tuan Nguyen.jpeg</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -4007,6 +4268,9 @@
       <c r="M88" t="str">
         <v>false</v>
       </c>
+      <c r="N88" t="str">
+        <v>William Lohmeier.jpeg</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -4048,6 +4312,9 @@
       <c r="M89" t="str">
         <v>false</v>
       </c>
+      <c r="N89" t="str">
+        <v>Zachary Owens.jpeg</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -4089,6 +4356,9 @@
       <c r="M90" t="str">
         <v>false</v>
       </c>
+      <c r="N90" t="str">
+        <v>Alex Anca.jpeg</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -4130,6 +4400,9 @@
       <c r="M91" t="str">
         <v>false</v>
       </c>
+      <c r="N91" t="str">
+        <v>Andrew Eberly.jpeg</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -4171,6 +4444,9 @@
       <c r="M92" t="str">
         <v>false</v>
       </c>
+      <c r="N92" t="str">
+        <v>Anthony Accardo.jpeg</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -4212,6 +4488,9 @@
       <c r="M93" t="str">
         <v>false</v>
       </c>
+      <c r="N93" t="str">
+        <v>Anton Massis.jpeg</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -4253,6 +4532,9 @@
       <c r="M94" t="str">
         <v>false</v>
       </c>
+      <c r="N94" t="str">
+        <v>Arsalan Amiri.jpeg</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -4294,6 +4576,9 @@
       <c r="M95" t="str">
         <v>false</v>
       </c>
+      <c r="N95" t="str">
+        <v>Aston Erickson.jpeg</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -4335,6 +4620,9 @@
       <c r="M96" t="str">
         <v>false</v>
       </c>
+      <c r="N96" t="str">
+        <v>Barron Beinke.jpeg</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -4376,6 +4664,9 @@
       <c r="M97" t="str">
         <v>false</v>
       </c>
+      <c r="N97" t="str">
+        <v>Charlie Preston.jpeg</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -4417,6 +4708,9 @@
       <c r="M98" t="str">
         <v>false</v>
       </c>
+      <c r="N98" t="str">
+        <v>Connor Prindiville.jpeg</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -4458,6 +4752,9 @@
       <c r="M99" t="str">
         <v>false</v>
       </c>
+      <c r="N99" t="str">
+        <v>Dominic Kauffman.jpeg</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -4499,6 +4796,9 @@
       <c r="M100" t="str">
         <v>false</v>
       </c>
+      <c r="N100" t="str">
+        <v>Garrett Paik.jpeg</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -4540,6 +4840,9 @@
       <c r="M101" t="str">
         <v>false</v>
       </c>
+      <c r="N101" t="str">
+        <v>Hank Petteys.jpeg</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -4581,6 +4884,9 @@
       <c r="M102" t="str">
         <v>false</v>
       </c>
+      <c r="N102" t="str">
+        <v>Harry Stonerock.jpeg</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -4622,6 +4928,9 @@
       <c r="M103" t="str">
         <v>false</v>
       </c>
+      <c r="N103" t="str">
+        <v>Jack McNamara.jpeg</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -4663,6 +4972,9 @@
       <c r="M104" t="str">
         <v>false</v>
       </c>
+      <c r="N104" t="str">
+        <v>Jacob Steele.jpeg</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -4704,6 +5016,9 @@
       <c r="M105" t="str">
         <v>false</v>
       </c>
+      <c r="N105" t="str">
+        <v>Jay Jaspar.jpeg</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -4745,6 +5060,9 @@
       <c r="M106" t="str">
         <v>false</v>
       </c>
+      <c r="N106" t="str">
+        <v>Leonardo Aguirre.jpeg</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -4786,6 +5104,9 @@
       <c r="M107" t="str">
         <v>false</v>
       </c>
+      <c r="N107" t="str">
+        <v>Liam St. John.jpeg</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -4827,6 +5148,9 @@
       <c r="M108" t="str">
         <v>false</v>
       </c>
+      <c r="N108" t="str">
+        <v>Luke Chandler.jpeg</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -4868,6 +5192,9 @@
       <c r="M109" t="str">
         <v>false</v>
       </c>
+      <c r="N109" t="str">
+        <v>Luke Schroeder.jpeg</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -4909,6 +5236,9 @@
       <c r="M110" t="str">
         <v>false</v>
       </c>
+      <c r="N110" t="str">
+        <v>Marek Turley.jpeg</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -4950,6 +5280,9 @@
       <c r="M111" t="str">
         <v>false</v>
       </c>
+      <c r="N111" t="str">
+        <v>Mateo Makhoul.jpeg</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -4991,6 +5324,9 @@
       <c r="M112" t="str">
         <v>false</v>
       </c>
+      <c r="N112" t="str">
+        <v>Matteus Owens.jpeg</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -5032,6 +5368,9 @@
       <c r="M113" t="str">
         <v>false</v>
       </c>
+      <c r="N113" t="str">
+        <v>Matthew Levy.jpeg</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -5073,6 +5412,9 @@
       <c r="M114" t="str">
         <v>false</v>
       </c>
+      <c r="N114" t="str">
+        <v>Matthew McClure.jpeg</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -5114,6 +5456,9 @@
       <c r="M115" t="str">
         <v>false</v>
       </c>
+      <c r="N115" t="str">
+        <v>Parker Lee.jpeg</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -5155,6 +5500,9 @@
       <c r="M116" t="str">
         <v>false</v>
       </c>
+      <c r="N116" t="str">
+        <v>Russell Tom.jpeg</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -5196,6 +5544,9 @@
       <c r="M117" t="str">
         <v>false</v>
       </c>
+      <c r="N117" t="str">
+        <v>Santino Voltattorni.jpeg</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -5237,6 +5588,9 @@
       <c r="M118" t="str">
         <v>false</v>
       </c>
+      <c r="N118" t="str">
+        <v>Sebastian Sera-Tacorda.jpeg</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -5278,6 +5632,9 @@
       <c r="M119" t="str">
         <v>false</v>
       </c>
+      <c r="N119" t="str">
+        <v>Tate Lustig.jpeg</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -5319,6 +5676,9 @@
       <c r="M120" t="str">
         <v>false</v>
       </c>
+      <c r="N120" t="str">
+        <v>Tolin Martell.jpeg</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -5360,10 +5720,13 @@
       <c r="M121" t="str">
         <v>false</v>
       </c>
+      <c r="N121" t="str">
+        <v>Zachary Hertstein.jpeg</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N121"/>
   </ignoredErrors>
 </worksheet>
 </file>